--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -6,6 +6,8 @@
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="ta.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="dm.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="ae.xpt" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -35,11 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -58,8 +56,23 @@
       <name val="Calibri"/>
       <i/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <i/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none">
         <bgColor/>
@@ -67,6 +80,24 @@
     </fill>
     <fill>
       <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -96,13 +127,15 @@
   <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -437,18 +470,18 @@
   <dimension ref="A1:B2"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="2" t="str">
         <v>Product</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="2" t="str">
         <v>Version</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="str">
+      <c r="A2" s="2" t="str">
         <v>sdtmig</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="2" t="str">
         <v>3-4</v>
       </c>
     </row>
@@ -461,69 +494,76 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="str">
+      <c r="A1" s="2" t="str">
         <v>Filename</v>
       </c>
-      <c r="B1" s="3" t="str">
+      <c r="B1" s="2" t="str">
         <v>Label</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="str">
+      <c r="A2" s="2" t="str">
         <v>ta.xpt</v>
       </c>
-      <c r="B2" s="3" t="str">
+      <c r="B2" s="2" t="str">
         <v>Trial Arms</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="str">
+        <v>dm.xpt</v>
+      </c>
+      <c r="B3" s="2" t="str">
+        <v>Demographics</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="str">
+        <v>ae.xpt</v>
+      </c>
+      <c r="B4" s="2" t="str">
+        <v>Adverse Events</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:G11"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="str">
+      <c r="A1" s="3" t="str">
         <v>STUDYID</v>
       </c>
-      <c r="B1" s="4" t="str">
+      <c r="B1" s="3" t="str">
         <v>DOMAIN</v>
       </c>
-      <c r="C1" s="4" t="str">
+      <c r="C1" s="3" t="str">
         <v>ARMCD</v>
       </c>
-      <c r="D1" s="4" t="str">
+      <c r="D1" s="3" t="str">
         <v>ARM</v>
       </c>
-      <c r="E1" s="4" t="str">
+      <c r="E1" s="3" t="str">
         <v>TAETORD</v>
       </c>
-      <c r="F1" s="4" t="str">
+      <c r="F1" s="3" t="str">
         <v>ETCD</v>
       </c>
-      <c r="G1" s="4" t="str">
+      <c r="G1" s="3" t="str">
         <v>ELEMENT</v>
       </c>
-      <c r="H1" s="4" t="str">
-        <v>TABRANCH</v>
-      </c>
-      <c r="I1" s="4" t="str">
-        <v>TATRANS</v>
-      </c>
-      <c r="J1" s="4" t="str">
-        <v>EPOCH</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="str">
+      <c r="A2" s="4" t="str">
         <v>Study Identifier</v>
       </c>
       <c r="B2" s="5" t="str">
@@ -532,351 +572,606 @@
       <c r="C2" s="5" t="str">
         <v>Planned Arm Code</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="6" t="str">
         <v>Description of Planned Arm</v>
       </c>
-      <c r="E2" s="5" t="str">
+      <c r="E2" s="6" t="str">
         <v>Planned Order of Element within Arm</v>
       </c>
-      <c r="F2" s="5" t="str">
+      <c r="F2" s="6" t="str">
         <v>Element Code</v>
       </c>
-      <c r="G2" s="5" t="str">
+      <c r="G2" s="6" t="str">
         <v>Description of Element</v>
       </c>
-      <c r="H2" s="5" t="str">
-        <v>Branch</v>
-      </c>
-      <c r="I2" s="5" t="str">
-        <v>Transition Rule</v>
-      </c>
-      <c r="J2" s="5" t="str">
-        <v>Epoch</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="B3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="C3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="D3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="E3" s="5" t="str">
+      <c r="A3" s="4" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="6" t="str">
         <v>Num</v>
       </c>
-      <c r="F3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="G3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="H3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="I3" s="5" t="str">
-        <v>Char</v>
-      </c>
-      <c r="J3" s="5" t="str">
+      <c r="F3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="G3" s="6" t="str">
         <v>Char</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="str">
+      <c r="A4" s="7">
         <v>12</v>
       </c>
-      <c r="B4" s="5" t="str">
+      <c r="B4" s="6">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="str">
+      <c r="C4" s="6">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6">
+        <v>40</v>
+      </c>
+      <c r="E4" s="6">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="str">
-        <v>28</v>
-      </c>
-      <c r="E4" s="5" t="str">
+      <c r="F4" s="6">
         <v>8</v>
       </c>
-      <c r="F4" s="5" t="str">
-        <v>7</v>
-      </c>
-      <c r="G4" s="5" t="str">
-        <v>26</v>
-      </c>
-      <c r="H4" s="5" t="str">
-        <v>200</v>
-      </c>
-      <c r="I4" s="5" t="str">
-        <v>200</v>
-      </c>
-      <c r="J4" s="5" t="str">
-        <v>9</v>
+      <c r="G4" s="6">
+        <v>40</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B5" s="3" t="str">
+      <c r="A5" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B5" s="2" t="str">
         <v>TA</v>
       </c>
-      <c r="C5" s="3" t="str">
-        <v>PLACEBO</v>
-      </c>
-      <c r="D5" s="3" t="str">
-        <v>Placebo</v>
-      </c>
-      <c r="E5" s="3" t="str">
+      <c r="C5" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <v>Drug A</v>
+      </c>
+      <c r="E5" s="2">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="str">
-        <v>SCREEN</v>
-      </c>
-      <c r="G5" s="3" t="str">
-        <v>Screening</v>
-      </c>
-      <c r="H5" s="3" t="str">
-        <v>Randomized to Placebo</v>
-      </c>
-      <c r="I5" s="3" t="str">
-        <v/>
-      </c>
-      <c r="J5" s="3" t="str">
-        <v>SCREENING</v>
+      <c r="F5" s="2" t="str">
+        <v>EL1</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>Element 1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B6" s="3" t="str">
+      <c r="A6" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B6" s="2" t="str">
         <v>TA</v>
       </c>
-      <c r="C6" s="3" t="str">
-        <v>PLACEBO</v>
-      </c>
-      <c r="D6" s="3" t="str">
-        <v>Placebo</v>
-      </c>
-      <c r="E6" s="3" t="str">
+      <c r="C6" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>Drug A</v>
+      </c>
+      <c r="E6" s="2">
         <v>2</v>
       </c>
-      <c r="F6" s="3" t="str">
-        <v>PLACEBO</v>
-      </c>
-      <c r="G6" s="3" t="str">
-        <v>Placebo</v>
-      </c>
-      <c r="H6" s="3" t="str">
-        <v/>
-      </c>
-      <c r="I6" s="3" t="str">
-        <v/>
-      </c>
-      <c r="J6" s="3" t="str">
-        <v>TREATMENT</v>
+      <c r="F6" s="2" t="str">
+        <v>EL2</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>Element 2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B7" s="3" t="str">
+      <c r="A7" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B7" s="2" t="str">
         <v>TA</v>
       </c>
-      <c r="C7" s="3" t="str">
-        <v>ZAN_LOW</v>
-      </c>
-      <c r="D7" s="3" t="str">
-        <v>Zanomaline Low Dose (54 mg)</v>
-      </c>
-      <c r="E7" s="3" t="str">
+      <c r="C7" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <v>Drug A</v>
+      </c>
+      <c r="E7" s="2">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <v>EL3</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>Element 3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>TA</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <v>Drug B</v>
+      </c>
+      <c r="E8" s="2">
         <v>1</v>
       </c>
-      <c r="F7" s="3" t="str">
-        <v>SCREEN</v>
-      </c>
-      <c r="G7" s="3" t="str">
-        <v>Screening</v>
-      </c>
-      <c r="H7" s="3" t="str">
-        <v>Randomized to Zanomaline Low Dose</v>
-      </c>
-      <c r="I7" s="3" t="str">
-        <v/>
-      </c>
-      <c r="J7" s="3" t="str">
-        <v>SCREENING</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B8" s="3" t="str">
+      <c r="F8" s="2" t="str">
+        <v>EL1</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>Element 1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B9" s="2" t="str">
         <v>TA</v>
       </c>
-      <c r="C8" s="3" t="str">
-        <v>ZAN_LOW</v>
-      </c>
-      <c r="D8" s="3" t="str">
-        <v>Zanomaline Low Dose (54 mg)</v>
-      </c>
-      <c r="E8" s="3" t="str">
+      <c r="C9" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <v>Drug B</v>
+      </c>
+      <c r="E9" s="2">
         <v>2</v>
       </c>
-      <c r="F8" s="3" t="str">
-        <v>LOW</v>
-      </c>
-      <c r="G8" s="3" t="str">
-        <v>Zanomaline 54 mg</v>
-      </c>
-      <c r="H8" s="3" t="str">
-        <v/>
-      </c>
-      <c r="I8" s="3" t="str">
-        <v/>
-      </c>
-      <c r="J8" s="3" t="str">
-        <v>TREATMENT</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B9" s="3" t="str">
+      <c r="F9" s="2" t="str">
+        <v>EL2</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>Element 2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B10" s="2" t="str">
         <v>TA</v>
       </c>
-      <c r="C9" s="3" t="str">
-        <v>ZAN_HIGH</v>
-      </c>
-      <c r="D9" s="3" t="str">
-        <v>Zanomaline High Dose (81 mg)</v>
-      </c>
-      <c r="E9" s="3" t="str">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3" t="str">
-        <v>SCREEN</v>
-      </c>
-      <c r="G9" s="3" t="str">
-        <v>Screening</v>
-      </c>
-      <c r="H9" s="3" t="str">
-        <v>Randomized to Zanomaline High Dose</v>
-      </c>
-      <c r="I9" s="3" t="str">
-        <v/>
-      </c>
-      <c r="J9" s="3" t="str">
-        <v>SCREENING</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B10" s="3" t="str">
+      <c r="C10" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <v>Drug B</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <v>EL3</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <v>Element 3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B11" s="2" t="str">
         <v>TA</v>
       </c>
-      <c r="C10" s="3" t="str">
-        <v>ZAN_HIGH</v>
-      </c>
-      <c r="D10" s="3" t="str">
-        <v>Zanomaline High Dose (81 mg)</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="str">
-        <v>TITRATE</v>
-      </c>
-      <c r="G10" s="3" t="str">
-        <v>Zanomaline 54 mg Titration</v>
-      </c>
-      <c r="H10" s="3" t="str">
-        <v/>
-      </c>
-      <c r="I10" s="3" t="str">
-        <v/>
-      </c>
-      <c r="J10" s="3" t="str">
-        <v>TREATMENT</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B11" s="3" t="str">
-        <v>TA</v>
-      </c>
-      <c r="C11" s="3" t="str">
-        <v>ZAN_HIGH</v>
-      </c>
-      <c r="D11" s="3" t="str">
-        <v>Zanomaline High Dose (81 mg)</v>
-      </c>
-      <c r="E11" s="3">
-        <v>3</v>
-      </c>
-      <c r="F11" s="3" t="str">
-        <v>HIGH</v>
-      </c>
-      <c r="G11" s="3" t="str">
-        <v>Zanomaline 81 mg</v>
-      </c>
-      <c r="H11" s="3" t="str">
-        <v/>
-      </c>
-      <c r="I11" s="3" t="str">
-        <v/>
-      </c>
-      <c r="J11" s="3" t="str">
-        <v>TREATMENT</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="str">
-        <v>CDISCPILOT01</v>
-      </c>
-      <c r="B12" s="3" t="str">
-        <v>TA</v>
-      </c>
-      <c r="C12" s="3" t="str">
-        <v>ZAN_HIGH</v>
-      </c>
-      <c r="D12" s="3" t="str">
-        <v>Zanomaline High Dose (81 mg)</v>
-      </c>
-      <c r="E12" s="3" t="str">
+      <c r="C11" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <v>Drug B</v>
+      </c>
+      <c r="E11" s="2">
         <v>4</v>
       </c>
-      <c r="F12" s="3" t="str">
-        <v>TITRATE</v>
-      </c>
-      <c r="G12" s="3" t="str">
-        <v>Zanomaline 54 mg Titration</v>
-      </c>
-      <c r="H12" s="3" t="str">
-        <v/>
-      </c>
-      <c r="I12" s="3" t="str">
-        <v/>
-      </c>
-      <c r="J12" s="3" t="str">
-        <v>TREATMENT</v>
+      <c r="F11" s="2" t="str">
+        <v>EL4</v>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>Element 4</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>ARMCD</v>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v>ARM</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="6" t="str">
+        <v>Unique Subject Identifier</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <v>Planned Arm Code</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <v>Description of Planned Arm</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <v>Char</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6">
+        <v>20</v>
+      </c>
+      <c r="E4" s="6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <v>SUBJ001</v>
+      </c>
+      <c r="D5" s="2" t="str">
+        <v>A</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <v>Drug A</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>DM</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>SUBJ002</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <v>B</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>Drug B</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G11"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="str">
+        <v>STUDYID</v>
+      </c>
+      <c r="B1" s="3" t="str">
+        <v>DOMAIN</v>
+      </c>
+      <c r="C1" s="3" t="str">
+        <v>USUBJID</v>
+      </c>
+      <c r="D1" s="3" t="str">
+        <v>AESEQ</v>
+      </c>
+      <c r="E1" s="3" t="str">
+        <v>AETERM</v>
+      </c>
+      <c r="F1" s="3" t="str">
+        <v>TAETORD</v>
+      </c>
+      <c r="G1" s="3" t="str">
+        <v>AESTDTC</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="str">
+        <v>Study Identifier</v>
+      </c>
+      <c r="B2" s="6" t="str">
+        <v>Domain Abbreviation</v>
+      </c>
+      <c r="C2" s="6" t="str">
+        <v>Unique Subject Identifier</v>
+      </c>
+      <c r="D2" s="6" t="str">
+        <v>Sequence Number</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <v>Reported Term for the Adverse Event</v>
+      </c>
+      <c r="F2" s="6" t="str">
+        <v>Planned Order of Element within Arm</v>
+      </c>
+      <c r="G2" s="6" t="str">
+        <v>Start Date/Time of Adverse Event</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="B3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="C3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="D3" s="6" t="str">
+        <v>Num</v>
+      </c>
+      <c r="E3" s="6" t="str">
+        <v>Char</v>
+      </c>
+      <c r="F3" s="6" t="str">
+        <v>Num</v>
+      </c>
+      <c r="G3" s="6" t="str">
+        <v>Char</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6">
+        <v>40</v>
+      </c>
+      <c r="F4" s="6">
+        <v>8</v>
+      </c>
+      <c r="G4" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B5" s="2" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C5" s="2" t="str">
+        <v>SUBJ001</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <v>EVENT 1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="str">
+        <v>2020-01-01</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B6" s="2" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <v>SUBJ001</v>
+      </c>
+      <c r="D6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <v>EVENT 2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2" t="str">
+        <v>2020-01-02</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B7" s="2" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <v>SUBJ001</v>
+      </c>
+      <c r="D7" s="2">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <v>EVENT 3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2" t="str">
+        <v>2020-01-03</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B8" s="2" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C8" s="2" t="str">
+        <v>SUBJ002</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <v>EVENT 4</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="str">
+        <v>2020-01-01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B9" s="2" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C9" s="2" t="str">
+        <v>SUBJ002</v>
+      </c>
+      <c r="D9" s="2">
+        <v>5</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <v>EVENT 5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2" t="str">
+        <v>2020-01-02</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B10" s="2" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C10" s="2" t="str">
+        <v>SUBJ002</v>
+      </c>
+      <c r="D10" s="2">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <v>EVENT 6</v>
+      </c>
+      <c r="F10" s="2">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2" t="str">
+        <v>2020-01-03</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="str">
+        <v>STUDY01</v>
+      </c>
+      <c r="B11" s="2" t="str">
+        <v>AE</v>
+      </c>
+      <c r="C11" s="2" t="str">
+        <v>SUBJ002</v>
+      </c>
+      <c r="D11" s="2">
+        <v>7</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <v>EVENT 7</v>
+      </c>
+      <c r="F11" s="2">
+        <v>4</v>
+      </c>
+      <c r="G11" s="2" t="str">
+        <v>2020-01-04</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,16 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\NEW-RULE\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3721AD-5338-4E36-A335-4C8D2F18B9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D057E37-E616-4E92-8F14-8BF572FCFD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21240" windowHeight="15270" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
     <sheet name="ti.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 

--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,38 +1,409 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\NEW-RULE\positive\01\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BD0A96-A502-479E-9515-1E5CB4DC5F0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21240" windowHeight="15270" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="dm.xpt" sheetId="3" r:id="rId3"/>
+    <sheet name="lb.xpt" sheetId="4" r:id="rId4"/>
+    <sheet name="xy.xpt" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="111">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>SUBJID</t>
+  </si>
+  <si>
+    <t>RFSTDTC</t>
+  </si>
+  <si>
+    <t>RFENDTC</t>
+  </si>
+  <si>
+    <t>RFXSTDTC</t>
+  </si>
+  <si>
+    <t>RFXENDTC</t>
+  </si>
+  <si>
+    <t>RFICDTC</t>
+  </si>
+  <si>
+    <t>RFPENDTC</t>
+  </si>
+  <si>
+    <t>DTHDTC</t>
+  </si>
+  <si>
+    <t>DTHFL</t>
+  </si>
+  <si>
+    <t>SITEID</t>
+  </si>
+  <si>
+    <t>AGE</t>
+  </si>
+  <si>
+    <t>AGEU</t>
+  </si>
+  <si>
+    <t>SEX</t>
+  </si>
+  <si>
+    <t>RACE</t>
+  </si>
+  <si>
+    <t>ARMCD</t>
+  </si>
+  <si>
+    <t>ARM</t>
+  </si>
+  <si>
+    <t>ACTARMCD</t>
+  </si>
+  <si>
+    <t>ACTARM</t>
+  </si>
+  <si>
+    <t>COUNTRY</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Subject Identifier for the Study</t>
+  </si>
+  <si>
+    <t>Subject Reference Start Date/Time</t>
+  </si>
+  <si>
+    <t>Subject Reference End Date/Time</t>
+  </si>
+  <si>
+    <t>Date/Time of First Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Last Study Treatment</t>
+  </si>
+  <si>
+    <t>Date/Time of Informed Consent</t>
+  </si>
+  <si>
+    <t>Date/Time of End of Participation</t>
+  </si>
+  <si>
+    <t>Date/Time of Death</t>
+  </si>
+  <si>
+    <t>Subject Death Flag</t>
+  </si>
+  <si>
+    <t>Study Site Identifier</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Age Units</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Race</t>
+  </si>
+  <si>
+    <t>Planned Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Planned Arm</t>
+  </si>
+  <si>
+    <t>Actual Arm Code</t>
+  </si>
+  <si>
+    <t>Description of Actual Arm</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>DM</t>
+  </si>
+  <si>
+    <t>CDISC-TEST-001</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>2012-11-30</t>
+  </si>
+  <si>
+    <t>2013-09-10</t>
+  </si>
+  <si>
+    <t>2012-10-25</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>YEARS</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>HUMAN INSULIN</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>LBSEQ</t>
+  </si>
+  <si>
+    <t>LBTESTCD</t>
+  </si>
+  <si>
+    <t>LBTEST</t>
+  </si>
+  <si>
+    <t>LBORRES</t>
+  </si>
+  <si>
+    <t>LBORRESU</t>
+  </si>
+  <si>
+    <t>VISITNUM</t>
+  </si>
+  <si>
+    <t>VISIT</t>
+  </si>
+  <si>
+    <t>LBDTC</t>
+  </si>
+  <si>
+    <t>LBDY</t>
+  </si>
+  <si>
+    <t>LBCHENDY</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Lab Test or Examination Short Name</t>
+  </si>
+  <si>
+    <t>Lab Test or Examination Name</t>
+  </si>
+  <si>
+    <t>Result or Finding in Original Units</t>
+  </si>
+  <si>
+    <t>Original Units</t>
+  </si>
+  <si>
+    <t>Visit Number</t>
+  </si>
+  <si>
+    <t>Visit Name</t>
+  </si>
+  <si>
+    <t>Date/Time of Specimen Collection</t>
+  </si>
+  <si>
+    <t>Study Day of Specimen Collection</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>LB</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>Albumin</t>
+  </si>
+  <si>
+    <t>mg/dL</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>DAY 1</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>XYSEQ</t>
+  </si>
+  <si>
+    <t>XYTESTCD</t>
+  </si>
+  <si>
+    <t>XYTEST</t>
+  </si>
+  <si>
+    <t>XYORRES</t>
+  </si>
+  <si>
+    <t>XYORRESU</t>
+  </si>
+  <si>
+    <t>XYDTC</t>
+  </si>
+  <si>
+    <t>XYDY</t>
+  </si>
+  <si>
+    <t>Custom Test Examination Short Name</t>
+  </si>
+  <si>
+    <t>Custom Test or Examination Name</t>
+  </si>
+  <si>
+    <t>XY</t>
+  </si>
+  <si>
+    <t>lb.xpt</t>
+  </si>
+  <si>
+    <t>Laboratory Test Results</t>
+  </si>
+  <si>
+    <t>dm.xpt</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>xy.xpt</t>
+  </si>
+  <si>
+    <t>Custom Domain</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -44,84 +415,32 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{353F7E92-F327-4232-83E7-82E01EED7A96}"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,36 +728,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -447,31 +754,847 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA6FF26-0BCC-490A-B215-BEBA7EE40340}">
+  <dimension ref="A1:V5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="2"/>
+    <col min="3" max="3" width="15" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="2"/>
+    <col min="5" max="10" width="13.140625" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3">
+        <v>10</v>
+      </c>
+      <c r="G4" s="3">
+        <v>10</v>
+      </c>
+      <c r="H4" s="3">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3">
+        <v>10</v>
+      </c>
+      <c r="J4" s="3">
+        <v>10</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3">
+        <v>3</v>
+      </c>
+      <c r="N4" s="3">
+        <v>8</v>
+      </c>
+      <c r="O4" s="3">
+        <v>5</v>
+      </c>
+      <c r="P4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3">
+        <v>1</v>
+      </c>
+      <c r="S4" s="3">
+        <v>13</v>
+      </c>
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3">
+        <v>13</v>
+      </c>
+      <c r="V4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="2">
+        <v>20121130</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5" s="2">
+        <v>26</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DA830A-13D3-4A40-8533-85C9903EBA35}">
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="3">
+        <v>8</v>
+      </c>
+      <c r="J4" s="3">
+        <v>18</v>
+      </c>
+      <c r="K4" s="3">
+        <v>10</v>
+      </c>
+      <c r="L4" s="3">
+        <v>8</v>
+      </c>
+      <c r="M4" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="4">
+        <v>2.12</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0A59EEB-1C4D-4648-9CFC-331CA7940714}">
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>14</v>
+      </c>
+      <c r="D4" s="3">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3">
+        <v>8</v>
+      </c>
+      <c r="F4" s="3">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I4" s="3">
+        <v>8</v>
+      </c>
+      <c r="J4" s="3">
+        <v>18</v>
+      </c>
+      <c r="K4" s="3">
+        <v>10</v>
+      </c>
+      <c r="L4" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxverisian/verisian/core-contributor/rules/NEW-RULE/positive/01/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\els_janssens\CORE\Rule_Authoring\core-contributor\rules\NEW-RULE\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C399113E-259D-5744-9B1B-03EBA8A1DBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C59F32-0FC3-4EF0-A222-60B7CE33E7F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="15300" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="64">
   <si>
     <t>Product</t>
   </si>
@@ -48,6 +48,18 @@
     <t>Findings About Events or Interventions</t>
   </si>
   <si>
+    <t>FATEST</t>
+  </si>
+  <si>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>FATESTCD</t>
+  </si>
+  <si>
+    <t>EPOCH</t>
+  </si>
+  <si>
     <t>STUDYID</t>
   </si>
   <si>
@@ -63,12 +75,6 @@
     <t>FAGRPID</t>
   </si>
   <si>
-    <t>FATESTCD</t>
-  </si>
-  <si>
-    <t>FATEST</t>
-  </si>
-  <si>
     <t>FAOBJ</t>
   </si>
   <si>
@@ -90,9 +96,6 @@
     <t>VISITNUM</t>
   </si>
   <si>
-    <t>EPOCH</t>
-  </si>
-  <si>
     <t>FADTC</t>
   </si>
   <si>
@@ -141,9 +144,6 @@
     <t>Visit Number</t>
   </si>
   <si>
-    <t>Epoch</t>
-  </si>
-  <si>
     <t>Date/Time of Collection</t>
   </si>
   <si>
@@ -171,12 +171,6 @@
     <t>CDISC001</t>
   </si>
   <si>
-    <t>SEV</t>
-  </si>
-  <si>
-    <t>Severity/Intensity</t>
-  </si>
-  <si>
     <t>ERYTHEMA</t>
   </si>
   <si>
@@ -198,19 +192,28 @@
     <t>2012-12-02</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>TOXGR</t>
-  </si>
-  <si>
-    <t>Toxicity</t>
-  </si>
-  <si>
-    <t>ASPIRINA</t>
-  </si>
-  <si>
-    <t>Y</t>
+    <t>CDISC002</t>
+  </si>
+  <si>
+    <t>2012-12-03</t>
+  </si>
+  <si>
+    <t>Occurence Indicator</t>
+  </si>
+  <si>
+    <t>Anatomical Region of Specimen</t>
+  </si>
+  <si>
+    <t>CDISC003</t>
+  </si>
+  <si>
+    <t>2012-12-04</t>
+  </si>
+  <si>
+    <t>BSANTREG</t>
+  </si>
+  <si>
+    <t>OCCUR</t>
   </si>
 </sst>
 </file>
@@ -227,29 +230,25 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -265,14 +264,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -281,21 +273,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1"/>
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1" xr:uid="{0554A65E-0FFC-D44E-B91B-C449F7DDF877}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -633,9 +623,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -643,7 +633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -662,9 +652,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -672,7 +662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -689,332 +679,397 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8B66B06-2F61-C644-9E2A-D867E7FC4CB7}">
-  <dimension ref="A1:Q6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Q7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="3"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="P2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>24</v>
+      <c r="G5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>41</v>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="5">
+      <c r="C7" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E7" s="4">
         <v>1</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F7" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="J7" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="L7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="N7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="L5" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O5" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="P5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="5">
-        <v>2</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H6" s="5" t="s">
+      <c r="P7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="M6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="O6" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q6" s="5">
-        <v>3</v>
+      <c r="Q7" s="4">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Q4 A5:E5 H5:Q5" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -1,38 +1,303 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\NEW-RULE\positive\01\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BA61A8-0ACB-4786-9F94-DCE3F0092205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Library" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datasets" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Library" sheetId="1" r:id="rId1"/>
+    <sheet name="Datasets" sheetId="2" r:id="rId2"/>
+    <sheet name="qs.xpt" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>sdtmig</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>Filename</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>qs.xpt</t>
+  </si>
+  <si>
+    <t>Questionnaires</t>
+  </si>
+  <si>
+    <t>STUDYID</t>
+  </si>
+  <si>
+    <t>DOMAIN</t>
+  </si>
+  <si>
+    <t>USUBJID</t>
+  </si>
+  <si>
+    <t>QSSEQ</t>
+  </si>
+  <si>
+    <t>QSTESTCD</t>
+  </si>
+  <si>
+    <t>QSTEST</t>
+  </si>
+  <si>
+    <t>QSCAT</t>
+  </si>
+  <si>
+    <t>QSORRES</t>
+  </si>
+  <si>
+    <t>QSSTRESC</t>
+  </si>
+  <si>
+    <t>QSSTRESN</t>
+  </si>
+  <si>
+    <t>QSLOBXFL</t>
+  </si>
+  <si>
+    <t>VISITNUM</t>
+  </si>
+  <si>
+    <t>VISIT</t>
+  </si>
+  <si>
+    <t>EPOCH</t>
+  </si>
+  <si>
+    <t>QSDTC</t>
+  </si>
+  <si>
+    <t>QSDY</t>
+  </si>
+  <si>
+    <t>QSEVLINT</t>
+  </si>
+  <si>
+    <t>Study Identifier</t>
+  </si>
+  <si>
+    <t>Domain Abbreviation</t>
+  </si>
+  <si>
+    <t>Unique Subject Identifier</t>
+  </si>
+  <si>
+    <t>Sequence Number</t>
+  </si>
+  <si>
+    <t>Question Short Name</t>
+  </si>
+  <si>
+    <t>Question Name</t>
+  </si>
+  <si>
+    <t>Category of Question</t>
+  </si>
+  <si>
+    <t>Finding in Original Units</t>
+  </si>
+  <si>
+    <t>Character Result/Finding in Std Format</t>
+  </si>
+  <si>
+    <t>Numeric Finding in Standard Units</t>
+  </si>
+  <si>
+    <t>Last Observation Before Exposure Flag</t>
+  </si>
+  <si>
+    <t>Visit Number</t>
+  </si>
+  <si>
+    <t>Visit Name</t>
+  </si>
+  <si>
+    <t>Epoch</t>
+  </si>
+  <si>
+    <t>Date/Time of Finding</t>
+  </si>
+  <si>
+    <t>Study Day of Finding</t>
+  </si>
+  <si>
+    <t>Evaluation Interval</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>CDISCPILOT01</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>CDISC001</t>
+  </si>
+  <si>
+    <t>PHQ0101</t>
+  </si>
+  <si>
+    <t>PHQ01-Little Interest/Pleasure in Things</t>
+  </si>
+  <si>
+    <t>PHQ-9</t>
+  </si>
+  <si>
+    <t>Several days</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>BASELINE</t>
+  </si>
+  <si>
+    <t>SCREENING</t>
+  </si>
+  <si>
+    <t>2012-11-30</t>
+  </si>
+  <si>
+    <t>PHQ0102</t>
+  </si>
+  <si>
+    <t>PHQ01-Feeling Down Depressed or Hopeless</t>
+  </si>
+  <si>
+    <t>Not at all</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>PHQ0103</t>
+  </si>
+  <si>
+    <t>PHQ01-Trouble Falling or Staying Asleep</t>
+  </si>
+  <si>
+    <t>PHQ0104</t>
+  </si>
+  <si>
+    <t>PHQ01-Feeling Tired or Little Energy</t>
+  </si>
+  <si>
+    <t>PHQ0105</t>
+  </si>
+  <si>
+    <t>PHQ01-Poor Appetite or Overeating</t>
+  </si>
+  <si>
+    <t>PHQ0106</t>
+  </si>
+  <si>
+    <t>PHQ01-Feeling Bad About Yourself</t>
+  </si>
+  <si>
+    <t>-P2M</t>
+  </si>
+  <si>
+    <t>2013-12-15T10:00/2013-12-15T20:00</t>
+  </si>
+  <si>
+    <t>2013-12-15T10:00/-P2D</t>
+  </si>
+  <si>
+    <t>P2W/2013-12-15T10:00</t>
+  </si>
+  <si>
+    <t>-P2D/P4W</t>
+  </si>
+  <si>
+    <t>P2W</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -47,81 +312,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -409,36 +620,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sdtmig</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>3-4</t>
-        </is>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -447,31 +646,570 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Filename</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Label</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A813908C-6C40-4ECC-9360-E46477389083}">
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="17" max="17" width="32.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>4</v>
+      </c>
+      <c r="C4" s="2">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7</v>
+      </c>
+      <c r="F4" s="2">
+        <v>40</v>
+      </c>
+      <c r="G4" s="2">
+        <v>5</v>
+      </c>
+      <c r="H4" s="2">
+        <v>23</v>
+      </c>
+      <c r="I4" s="2">
+        <v>20</v>
+      </c>
+      <c r="J4" s="2">
+        <v>8</v>
+      </c>
+      <c r="K4" s="2">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2">
+        <v>200</v>
+      </c>
+      <c r="N4" s="2">
+        <v>9</v>
+      </c>
+      <c r="O4" s="2">
+        <v>10</v>
+      </c>
+      <c r="P4" s="2">
+        <v>8</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="3">
+        <v>3</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="3">
+        <v>3</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="3">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L7" s="3">
+        <v>3</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="3">
+        <v>4</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8" s="3">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L9" s="3">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="3">
+        <v>6</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="3">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
+++ b/rules/NEW-RULE/positive/01/data/new-rule-positive-01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marisa_wyckmans\CORE\CDISC_Rule_Authoring\core-contributor\rules\NEW-RULE\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9BA61A8-0ACB-4786-9F94-DCE3F0092205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F142E9E4-1E21-405D-94EA-728DA567B09D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="71">
   <si>
     <t>Product</t>
   </si>
@@ -235,28 +235,19 @@
     <t>PHQ01-Poor Appetite or Overeating</t>
   </si>
   <si>
-    <t>PHQ0106</t>
-  </si>
-  <si>
-    <t>PHQ01-Feeling Bad About Yourself</t>
-  </si>
-  <si>
     <t>-P2M</t>
   </si>
   <si>
     <t>2013-12-15T10:00/2013-12-15T20:00</t>
   </si>
   <si>
-    <t>2013-12-15T10:00/-P2D</t>
-  </si>
-  <si>
     <t>P2W/2013-12-15T10:00</t>
   </si>
   <si>
-    <t>-P2D/P4W</t>
-  </si>
-  <si>
     <t>P2W</t>
+  </si>
+  <si>
+    <t>2013-12-15T10:00/P2D</t>
   </si>
 </sst>
 </file>
@@ -312,13 +303,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,7 +663,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A813908C-6C40-4ECC-9360-E46477389083}">
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="17" max="17" width="32.5703125" bestFit="1" customWidth="1"/>
@@ -941,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -994,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -1046,8 +1036,8 @@
       <c r="P7" s="3">
         <v>1</v>
       </c>
-      <c r="Q7" s="5" t="s">
-        <v>69</v>
+      <c r="Q7" s="3" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -1099,7 +1089,7 @@
       <c r="P8" s="3">
         <v>1</v>
       </c>
-      <c r="Q8" s="5" t="s">
+      <c r="Q8" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1152,61 +1142,8 @@
       <c r="P9" s="3">
         <v>1</v>
       </c>
-      <c r="Q9" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="3">
-        <v>6</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="L10" s="3">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>72</v>
+      <c r="Q9" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
